--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/3.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/3.xlsx
@@ -426,13 +426,13 @@
         <v>-1.095850475916783</v>
       </c>
       <c r="E2">
-        <v>-9.275265702996682</v>
+        <v>-6.693517406777491</v>
       </c>
       <c r="F2">
-        <v>-4.928384435714208</v>
+        <v>-5.847091930728222</v>
       </c>
       <c r="G2">
-        <v>-4.632908018341658</v>
+        <v>0.8597148219058008</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.765087181447526</v>
       </c>
       <c r="E3">
-        <v>-7.843990169445596</v>
+        <v>-7.364020149480461</v>
       </c>
       <c r="F3">
-        <v>-4.790461263148091</v>
+        <v>-6.216956319343396</v>
       </c>
       <c r="G3">
-        <v>-4.603941807103257</v>
+        <v>1.193759592338746</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.426071205633601</v>
       </c>
       <c r="E4">
-        <v>-8.864658465367508</v>
+        <v>-7.544090932891051</v>
       </c>
       <c r="F4">
-        <v>-4.895074954080237</v>
+        <v>-6.588619093590047</v>
       </c>
       <c r="G4">
-        <v>-4.782793476062063</v>
+        <v>0.8553705429061883</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.985625413728951</v>
       </c>
       <c r="E5">
-        <v>-9.800410202541979</v>
+        <v>-8.178311221460319</v>
       </c>
       <c r="F5">
-        <v>-5.468715238681881</v>
+        <v>-6.40055898396949</v>
       </c>
       <c r="G5">
-        <v>-4.695701647247115</v>
+        <v>0.4811176950255077</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.434553797583877</v>
       </c>
       <c r="E6">
-        <v>-10.76993170099863</v>
+        <v>-8.708730299388147</v>
       </c>
       <c r="F6">
-        <v>-5.074771866402132</v>
+        <v>-6.120031534644035</v>
       </c>
       <c r="G6">
-        <v>-4.125076423456667</v>
+        <v>-0.1914179438790481</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.741545190278034</v>
       </c>
       <c r="E7">
-        <v>-11.63986749830854</v>
+        <v>-9.942437570217139</v>
       </c>
       <c r="F7">
-        <v>-4.846704924695969</v>
+        <v>-6.221904157840318</v>
       </c>
       <c r="G7">
-        <v>-6.268641323713186</v>
+        <v>-0.02851009213817016</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.900465372175627</v>
       </c>
       <c r="E8">
-        <v>-11.18965939069713</v>
+        <v>-9.459751350045567</v>
       </c>
       <c r="F8">
-        <v>-5.314792149730691</v>
+        <v>-6.219317166441375</v>
       </c>
       <c r="G8">
-        <v>-5.314361960769458</v>
+        <v>-0.9795912929577846</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.904171871692381</v>
       </c>
       <c r="E9">
-        <v>-12.36705326917277</v>
+        <v>-9.899601348612858</v>
       </c>
       <c r="F9">
-        <v>-5.050733472740292</v>
+        <v>-6.084010806500701</v>
       </c>
       <c r="G9">
-        <v>-6.109203151533897</v>
+        <v>-1.421055149592086</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.760660845465119</v>
       </c>
       <c r="E10">
-        <v>-12.12649511602737</v>
+        <v>-10.6373445826648</v>
       </c>
       <c r="F10">
-        <v>-4.503345807868171</v>
+        <v>-5.991759670687934</v>
       </c>
       <c r="G10">
-        <v>-5.541235665737202</v>
+        <v>-0.8989140636032018</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.487279243113852</v>
       </c>
       <c r="E11">
-        <v>-13.84225731890657</v>
+        <v>-11.35462909773064</v>
       </c>
       <c r="F11">
-        <v>-4.68074814248431</v>
+        <v>-6.156020784826062</v>
       </c>
       <c r="G11">
-        <v>-5.061916012531758</v>
+        <v>-1.340304819388952</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.113711801328878</v>
       </c>
       <c r="E12">
-        <v>-13.14818094872387</v>
+        <v>-12.23463643250326</v>
       </c>
       <c r="F12">
-        <v>-3.869139440610841</v>
+        <v>-5.888303209017498</v>
       </c>
       <c r="G12">
-        <v>-5.821898541515654</v>
+        <v>-1.078454969134063</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.675381445689754</v>
       </c>
       <c r="E13">
-        <v>-14.66487973280403</v>
+        <v>-12.39128725725314</v>
       </c>
       <c r="F13">
-        <v>-4.45835137565031</v>
+        <v>-5.359590258874088</v>
       </c>
       <c r="G13">
-        <v>-3.777615036569991</v>
+        <v>-0.6561957497119908</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.217615109344878</v>
       </c>
       <c r="E14">
-        <v>-15.50006145774778</v>
+        <v>-13.7511981606097</v>
       </c>
       <c r="F14">
-        <v>-4.998588573101467</v>
+        <v>-5.387116907669116</v>
       </c>
       <c r="G14">
-        <v>-4.704959347567203</v>
+        <v>-0.3234093581719625</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.782996532779356</v>
       </c>
       <c r="E15">
-        <v>-17.68513238712127</v>
+        <v>-14.09535817025294</v>
       </c>
       <c r="F15">
-        <v>-3.816346757663026</v>
+        <v>-4.87186824129081</v>
       </c>
       <c r="G15">
-        <v>-3.105523224245924</v>
+        <v>0.1427782497401814</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.409914381964705</v>
       </c>
       <c r="E16">
-        <v>-14.90358140048723</v>
+        <v>-15.58832550482303</v>
       </c>
       <c r="F16">
-        <v>-3.869521317983532</v>
+        <v>-4.565204143672224</v>
       </c>
       <c r="G16">
-        <v>-4.164052229457397</v>
+        <v>0.01405809841993197</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.134152156328337</v>
       </c>
       <c r="E17">
-        <v>-17.3984943543269</v>
+        <v>-15.1052779552662</v>
       </c>
       <c r="F17">
-        <v>-3.888602761107018</v>
+        <v>-4.534736790597258</v>
       </c>
       <c r="G17">
-        <v>-3.509327090153416</v>
+        <v>0.7361691663651379</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.9736249928666664</v>
       </c>
       <c r="E18">
-        <v>-18.55726108001069</v>
+        <v>-16.9923642785059</v>
       </c>
       <c r="F18">
-        <v>-3.497134550626834</v>
+        <v>-3.887434763069071</v>
       </c>
       <c r="G18">
-        <v>-3.837795310139743</v>
+        <v>1.197409413277122</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.9376330752241382</v>
       </c>
       <c r="E19">
-        <v>-20.30562599178979</v>
+        <v>-17.59220013051691</v>
       </c>
       <c r="F19">
-        <v>-2.801984365178142</v>
+        <v>-3.769670739617482</v>
       </c>
       <c r="G19">
-        <v>-1.83665958105141</v>
+        <v>1.548050687075774</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.024914130533849</v>
       </c>
       <c r="E20">
-        <v>-19.1736225598832</v>
+        <v>-17.83709838949675</v>
       </c>
       <c r="F20">
-        <v>-2.757255010529177</v>
+        <v>-3.442471414083497</v>
       </c>
       <c r="G20">
-        <v>-2.213685039687852</v>
+        <v>1.980833817944623</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.215137148491386</v>
       </c>
       <c r="E21">
-        <v>-21.68960475477373</v>
+        <v>-19.91132010861057</v>
       </c>
       <c r="F21">
-        <v>-2.642448258705582</v>
+        <v>-3.229265383583558</v>
       </c>
       <c r="G21">
-        <v>-1.996612069915147</v>
+        <v>2.02479614611438</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.489166616854363</v>
       </c>
       <c r="E22">
-        <v>-21.21733894181615</v>
+        <v>-20.22993371539479</v>
       </c>
       <c r="F22">
-        <v>-2.283425542658248</v>
+        <v>-2.910623093320492</v>
       </c>
       <c r="G22">
-        <v>-0.9458421976284631</v>
+        <v>2.543916600611346</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.821512361997063</v>
       </c>
       <c r="E23">
-        <v>-22.09276113128616</v>
+        <v>-20.30999932331483</v>
       </c>
       <c r="F23">
-        <v>-1.438787347332955</v>
+        <v>-2.890367853587238</v>
       </c>
       <c r="G23">
-        <v>-1.767895179266077</v>
+        <v>2.267877353503756</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.180578690653588</v>
       </c>
       <c r="E24">
-        <v>-22.17547233482012</v>
+        <v>-21.07401992541897</v>
       </c>
       <c r="F24">
-        <v>-1.798935814680693</v>
+        <v>-2.465094797766208</v>
       </c>
       <c r="G24">
-        <v>-1.893555537925541</v>
+        <v>2.267678936914831</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.545560548072615</v>
       </c>
       <c r="E25">
-        <v>-22.26163070375369</v>
+        <v>-21.46069635939448</v>
       </c>
       <c r="F25">
-        <v>-1.372435118368715</v>
+        <v>-2.518951932826621</v>
       </c>
       <c r="G25">
-        <v>-2.165255727522701</v>
+        <v>2.534525752317111</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.894294374661631</v>
       </c>
       <c r="E26">
-        <v>-23.32691279572691</v>
+        <v>-20.89649921376182</v>
       </c>
       <c r="F26">
-        <v>-1.184517487941438</v>
+        <v>-2.565242760029863</v>
       </c>
       <c r="G26">
-        <v>-1.880225076043317</v>
+        <v>2.379053301171724</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.206000820078774</v>
       </c>
       <c r="E27">
-        <v>-22.11594435690135</v>
+        <v>-21.44223118184429</v>
       </c>
       <c r="F27">
-        <v>-0.627299587100295</v>
+        <v>-2.121184816615548</v>
       </c>
       <c r="G27">
-        <v>-1.978172380868114</v>
+        <v>2.404539389870172</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.469255565300417</v>
       </c>
       <c r="E28">
-        <v>-23.08829834548154</v>
+        <v>-21.12390414664148</v>
       </c>
       <c r="F28">
-        <v>-1.262466032177469</v>
+        <v>-2.292602196746461</v>
       </c>
       <c r="G28">
-        <v>-1.528082624104775</v>
+        <v>2.116109548933158</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.672145935197983</v>
       </c>
       <c r="E29">
-        <v>-21.05772272418034</v>
+        <v>-22.35971294240084</v>
       </c>
       <c r="F29">
-        <v>-0.6973405361092015</v>
+        <v>-2.550542552099783</v>
       </c>
       <c r="G29">
-        <v>-2.530297868485934</v>
+        <v>1.519700611560875</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.80770527037228</v>
       </c>
       <c r="E30">
-        <v>-23.7660941272709</v>
+        <v>-21.04373886164964</v>
       </c>
       <c r="F30">
-        <v>-1.320471631191102</v>
+        <v>-2.722695522484381</v>
       </c>
       <c r="G30">
-        <v>-1.601029438725071</v>
+        <v>2.170029256973421</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.876566980883922</v>
       </c>
       <c r="E31">
-        <v>-21.63502740475415</v>
+        <v>-20.86230997813583</v>
       </c>
       <c r="F31">
-        <v>-1.030327664686547</v>
+        <v>-2.634799942475535</v>
       </c>
       <c r="G31">
-        <v>-1.017475807719429</v>
+        <v>2.0538746193702</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.879467496156404</v>
       </c>
       <c r="E32">
-        <v>-23.18451994545516</v>
+        <v>-20.47800918103812</v>
       </c>
       <c r="F32">
-        <v>-1.372720076755278</v>
+        <v>-2.916001682866868</v>
       </c>
       <c r="G32">
-        <v>-1.920874369326951</v>
+        <v>1.899232385004787</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.821728238811341</v>
       </c>
       <c r="E33">
-        <v>-22.21131870176471</v>
+        <v>-20.54027827843128</v>
       </c>
       <c r="F33">
-        <v>-2.610781429631363</v>
+        <v>-3.07622781938596</v>
       </c>
       <c r="G33">
-        <v>-0.7800834127940895</v>
+        <v>2.384598522683249</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.711306430235664</v>
       </c>
       <c r="E34">
-        <v>-22.06503013927028</v>
+        <v>-19.15325936475756</v>
       </c>
       <c r="F34">
-        <v>-1.137255814142115</v>
+        <v>-2.943747020656235</v>
       </c>
       <c r="G34">
-        <v>-1.020138767202365</v>
+        <v>2.423994658563148</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.553539677383196</v>
       </c>
       <c r="E35">
-        <v>-21.34187298339113</v>
+        <v>-19.61171990327141</v>
       </c>
       <c r="F35">
-        <v>-1.7988786573299</v>
+        <v>-2.972772186082927</v>
       </c>
       <c r="G35">
-        <v>-0.6308062585634141</v>
+        <v>2.329362999369065</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.358578785151823</v>
       </c>
       <c r="E36">
-        <v>-20.35451759550567</v>
+        <v>-19.46949318145266</v>
       </c>
       <c r="F36">
-        <v>-1.663661761068729</v>
+        <v>-2.905764718503072</v>
       </c>
       <c r="G36">
-        <v>-0.9249249119644635</v>
+        <v>3.086557253129651</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.136061499638092</v>
       </c>
       <c r="E37">
-        <v>-19.9947622773377</v>
+        <v>-18.00322684248989</v>
       </c>
       <c r="F37">
-        <v>-1.613545533199358</v>
+        <v>-2.932202892530821</v>
       </c>
       <c r="G37">
-        <v>-0.8131719897418593</v>
+        <v>2.984184736222917</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.891764838993701</v>
       </c>
       <c r="E38">
-        <v>-19.35270072578715</v>
+        <v>-17.95031077700025</v>
       </c>
       <c r="F38">
-        <v>-1.947885385745475</v>
+        <v>-2.956906465217108</v>
       </c>
       <c r="G38">
-        <v>0.3633522280095696</v>
+        <v>3.017531776885207</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.638025827200569</v>
       </c>
       <c r="E39">
-        <v>-19.22891010903932</v>
+        <v>-17.5227293646865</v>
       </c>
       <c r="F39">
-        <v>-1.851118819220048</v>
+        <v>-2.853900635413795</v>
       </c>
       <c r="G39">
-        <v>0.2610893623756622</v>
+        <v>3.490990308483601</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.384855838576311</v>
       </c>
       <c r="E40">
-        <v>-19.4337880236931</v>
+        <v>-17.50376580177733</v>
       </c>
       <c r="F40">
-        <v>-1.349906838482179</v>
+        <v>-2.486200770822137</v>
       </c>
       <c r="G40">
-        <v>-0.4255808477451809</v>
+        <v>3.982643119137464</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.139252229642996</v>
       </c>
       <c r="E41">
-        <v>-17.00799281272123</v>
+        <v>-16.68166253929547</v>
       </c>
       <c r="F41">
-        <v>-1.299009460151969</v>
+        <v>-2.55908136328784</v>
       </c>
       <c r="G41">
-        <v>0.8864096853499341</v>
+        <v>3.825797416337152</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.916706032832764</v>
       </c>
       <c r="E42">
-        <v>-19.20239600794161</v>
+        <v>-17.12895509255686</v>
       </c>
       <c r="F42">
-        <v>-1.715871273364973</v>
+        <v>-2.664832402664031</v>
       </c>
       <c r="G42">
-        <v>0.8553574891832327</v>
+        <v>4.259374213561699</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.726506150360721</v>
       </c>
       <c r="E43">
-        <v>-16.45608086618741</v>
+        <v>-15.99641174317804</v>
       </c>
       <c r="F43">
-        <v>-1.16519581827114</v>
+        <v>-2.779077521388527</v>
       </c>
       <c r="G43">
-        <v>0.3900000980510629</v>
+        <v>4.270362837545695</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.57661114550424</v>
       </c>
       <c r="E44">
-        <v>-17.37001578427256</v>
+        <v>-15.67629882710555</v>
       </c>
       <c r="F44">
-        <v>-0.4827850951101016</v>
+        <v>-2.386961527599353</v>
       </c>
       <c r="G44">
-        <v>1.579147265900525</v>
+        <v>4.173211809821187</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.479843502129464</v>
       </c>
       <c r="E45">
-        <v>-16.40986808377604</v>
+        <v>-15.3294599961578</v>
       </c>
       <c r="F45">
-        <v>-1.773158677840378</v>
+        <v>-2.637539353476592</v>
       </c>
       <c r="G45">
-        <v>1.778130386401406</v>
+        <v>4.71404060559326</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.439411881624101</v>
       </c>
       <c r="E46">
-        <v>-16.58547831822377</v>
+        <v>-15.40552190836071</v>
       </c>
       <c r="F46">
-        <v>-1.739334780049269</v>
+        <v>-2.329436381679344</v>
       </c>
       <c r="G46">
-        <v>1.416829442437238</v>
+        <v>5.011386139308925</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.459179452692938</v>
       </c>
       <c r="E47">
-        <v>-18.13849278212823</v>
+        <v>-14.54922110383021</v>
       </c>
       <c r="F47">
-        <v>-1.865128997103596</v>
+        <v>-2.268354226131714</v>
       </c>
       <c r="G47">
-        <v>1.574682892649721</v>
+        <v>5.06479414140933</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.542951795313463</v>
       </c>
       <c r="E48">
-        <v>-14.15529731609287</v>
+        <v>-14.68010540552085</v>
       </c>
       <c r="F48">
-        <v>-1.138099920525568</v>
+        <v>-2.708265362327614</v>
       </c>
       <c r="G48">
-        <v>1.067668460821747</v>
+        <v>5.579920156681893</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.683420235427004</v>
       </c>
       <c r="E49">
-        <v>-15.08354004719205</v>
+        <v>-14.50503093533403</v>
       </c>
       <c r="F49">
-        <v>-1.896946589045125</v>
+        <v>-2.206846289739045</v>
       </c>
       <c r="G49">
-        <v>1.299724493802852</v>
+        <v>4.78420436647943</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.876460833441571</v>
       </c>
       <c r="E50">
-        <v>-14.0583489041374</v>
+        <v>-13.01276549347784</v>
       </c>
       <c r="F50">
-        <v>-1.794763328072792</v>
+        <v>-2.563248879691324</v>
       </c>
       <c r="G50">
-        <v>1.691116879924191</v>
+        <v>4.815032038611295</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.113714777876438</v>
       </c>
       <c r="E51">
-        <v>-14.63033747421543</v>
+        <v>-13.32117466003695</v>
       </c>
       <c r="F51">
-        <v>-1.408859261437212</v>
+        <v>-2.647816079475723</v>
       </c>
       <c r="G51">
-        <v>1.576993401612856</v>
+        <v>4.830800935941619</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.377991575694192</v>
       </c>
       <c r="E52">
-        <v>-14.76844421039996</v>
+        <v>-13.39606951985759</v>
       </c>
       <c r="F52">
-        <v>-0.6992234152157648</v>
+        <v>-2.396625261720412</v>
       </c>
       <c r="G52">
-        <v>1.04225286222726</v>
+        <v>4.732482905384884</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.659525639864939</v>
       </c>
       <c r="E53">
-        <v>-14.31000028473141</v>
+        <v>-12.01140963021638</v>
       </c>
       <c r="F53">
-        <v>-1.516296028478099</v>
+        <v>-2.418919941999358</v>
       </c>
       <c r="G53">
-        <v>1.150489111485634</v>
+        <v>4.143245683404389</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.944448071396265</v>
       </c>
       <c r="E54">
-        <v>-14.20755717419319</v>
+        <v>-11.68457681822032</v>
       </c>
       <c r="F54">
-        <v>-1.379853976828187</v>
+        <v>-2.566346145410392</v>
       </c>
       <c r="G54">
-        <v>1.428306275659772</v>
+        <v>4.384005938852265</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.216253524979859</v>
       </c>
       <c r="E55">
-        <v>-13.43248072354236</v>
+        <v>-11.99426932707881</v>
       </c>
       <c r="F55">
-        <v>-1.784948002717021</v>
+        <v>-2.516195126110104</v>
       </c>
       <c r="G55">
-        <v>1.346381110390637</v>
+        <v>3.821259942237797</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.46734162924073</v>
       </c>
       <c r="E56">
-        <v>-13.09154360588718</v>
+        <v>-11.75811357793773</v>
       </c>
       <c r="F56">
-        <v>-1.630031701249874</v>
+        <v>-2.350534071061245</v>
       </c>
       <c r="G56">
-        <v>0.9932779044425654</v>
+        <v>4.183584298081681</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.68726319220247</v>
       </c>
       <c r="E57">
-        <v>-13.59794881593485</v>
+        <v>-11.21969126178696</v>
       </c>
       <c r="F57">
-        <v>-1.203526034733479</v>
+        <v>-2.404475699596743</v>
       </c>
       <c r="G57">
-        <v>0.8520862262105677</v>
+        <v>3.452604530760463</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.867856894053953</v>
       </c>
       <c r="E58">
-        <v>-13.26319998315367</v>
+        <v>-11.77259167261609</v>
       </c>
       <c r="F58">
-        <v>-1.614943817375284</v>
+        <v>-2.233398778468381</v>
       </c>
       <c r="G58">
-        <v>0.2867033775590746</v>
+        <v>3.565485294646428</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.008919907791573</v>
       </c>
       <c r="E59">
-        <v>-12.83391575419675</v>
+        <v>-10.00589033283787</v>
       </c>
       <c r="F59">
-        <v>-1.356485732395213</v>
+        <v>-2.494625267308608</v>
       </c>
       <c r="G59">
-        <v>0.2532754038144601</v>
+        <v>3.549066321912917</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.107325793994931</v>
       </c>
       <c r="E60">
-        <v>-12.45786738800147</v>
+        <v>-10.31602723530812</v>
       </c>
       <c r="F60">
-        <v>-1.410560728082562</v>
+        <v>-2.309492608089543</v>
       </c>
       <c r="G60">
-        <v>0.1253567510836824</v>
+        <v>3.45581052511835</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.165120018579342</v>
       </c>
       <c r="E61">
-        <v>-11.7650494408502</v>
+        <v>-10.69510744577052</v>
       </c>
       <c r="F61">
-        <v>-1.803098360879761</v>
+        <v>-2.652188202627699</v>
       </c>
       <c r="G61">
-        <v>-0.3782793772433904</v>
+        <v>3.554974436922606</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.190059115942018</v>
       </c>
       <c r="E62">
-        <v>-11.13309265245296</v>
+        <v>-9.584945752221198</v>
       </c>
       <c r="F62">
-        <v>-1.291353688615296</v>
+        <v>-2.54830761684703</v>
       </c>
       <c r="G62">
-        <v>-0.5455837228757031</v>
+        <v>2.965760711643431</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.185617083355909</v>
       </c>
       <c r="E63">
-        <v>-10.12978062665751</v>
+        <v>-9.718438270623837</v>
       </c>
       <c r="F63">
-        <v>-1.604981042621814</v>
+        <v>-2.393388001910272</v>
       </c>
       <c r="G63">
-        <v>-0.5869379171989375</v>
+        <v>2.278876420466116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.162501708952513</v>
       </c>
       <c r="E64">
-        <v>-10.72967877683839</v>
+        <v>-9.656949976959751</v>
       </c>
       <c r="F64">
-        <v>-1.796261844704456</v>
+        <v>-2.659834033755538</v>
       </c>
       <c r="G64">
-        <v>-1.012593715334048</v>
+        <v>2.341696156817484</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.131044401717698</v>
       </c>
       <c r="E65">
-        <v>-10.29101244349867</v>
+        <v>-9.155831804928589</v>
       </c>
       <c r="F65">
-        <v>-1.927267321089795</v>
+        <v>-2.354651885420561</v>
       </c>
       <c r="G65">
-        <v>-1.288760888926602</v>
+        <v>1.835731244315138</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.093549060206256</v>
       </c>
       <c r="E66">
-        <v>-10.91082939519344</v>
+        <v>-9.227827723244491</v>
       </c>
       <c r="F66">
-        <v>-1.715421469865253</v>
+        <v>-2.507927191062762</v>
       </c>
       <c r="G66">
-        <v>-1.690141983853541</v>
+        <v>2.236522310964485</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.059025977330986</v>
       </c>
       <c r="E67">
-        <v>-9.163145610071611</v>
+        <v>-9.396398264496632</v>
       </c>
       <c r="F67">
-        <v>-2.374690092894281</v>
+        <v>-2.751353721151633</v>
       </c>
       <c r="G67">
-        <v>-1.205355431474306</v>
+        <v>1.646608906134892</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.029754830156586</v>
       </c>
       <c r="E68">
-        <v>-9.656156713596708</v>
+        <v>-9.276449368224259</v>
       </c>
       <c r="F68">
-        <v>-1.512816885386341</v>
+        <v>-2.795381448610427</v>
       </c>
       <c r="G68">
-        <v>-1.519621200884977</v>
+        <v>1.696991055254196</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.000748189835247</v>
       </c>
       <c r="E69">
-        <v>-9.978163494033314</v>
+        <v>-8.32751118509346</v>
       </c>
       <c r="F69">
-        <v>-2.523087971268799</v>
+        <v>-2.921332227103883</v>
       </c>
       <c r="G69">
-        <v>-2.192647659772662</v>
+        <v>1.717997106234294</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.973846900889125</v>
       </c>
       <c r="E70">
-        <v>-9.818713404850497</v>
+        <v>-8.732926908566597</v>
       </c>
       <c r="F70">
-        <v>-2.317406001888487</v>
+        <v>-3.079638207983286</v>
       </c>
       <c r="G70">
-        <v>-2.371146878211668</v>
+        <v>1.360949065209049</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.942579063529373</v>
       </c>
       <c r="E71">
-        <v>-8.904458689493341</v>
+        <v>-9.185377750293419</v>
       </c>
       <c r="F71">
-        <v>-2.327370433376762</v>
+        <v>-3.062183678438897</v>
       </c>
       <c r="G71">
-        <v>-1.761451861615209</v>
+        <v>1.312658122507227</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.897691836611997</v>
       </c>
       <c r="E72">
-        <v>-9.410697771088017</v>
+        <v>-8.298064916800426</v>
       </c>
       <c r="F72">
-        <v>-1.835176060185769</v>
+        <v>-3.074066608832056</v>
       </c>
       <c r="G72">
-        <v>-1.598366479242135</v>
+        <v>1.778621206384535</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.836521674168915</v>
       </c>
       <c r="E73">
-        <v>-7.915138832651233</v>
+        <v>-8.710017794898842</v>
       </c>
       <c r="F73">
-        <v>-2.730188105642703</v>
+        <v>-3.36200297620815</v>
       </c>
       <c r="G73">
-        <v>-0.4964808386060444</v>
+        <v>1.261315219378393</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.749803488948637</v>
       </c>
       <c r="E74">
-        <v>-10.4242682288558</v>
+        <v>-8.770754357313136</v>
       </c>
       <c r="F74">
-        <v>-2.493943520936104</v>
+        <v>-3.330957422686031</v>
       </c>
       <c r="G74">
-        <v>-1.933620024420766</v>
+        <v>1.708055390831334</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.631223140756105</v>
       </c>
       <c r="E75">
-        <v>-9.580119720661747</v>
+        <v>-9.569977578606517</v>
       </c>
       <c r="F75">
-        <v>-2.542744301369828</v>
+        <v>-3.672927367379334</v>
       </c>
       <c r="G75">
-        <v>-1.197126364523117</v>
+        <v>1.307146840675387</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.479138124472666</v>
       </c>
       <c r="E76">
-        <v>-9.647368518433371</v>
+        <v>-9.615338952696293</v>
       </c>
       <c r="F76">
-        <v>-3.331530652928768</v>
+        <v>-3.642127010608442</v>
       </c>
       <c r="G76">
-        <v>-2.316201147547098</v>
+        <v>1.019735190128907</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.288469677220593</v>
       </c>
       <c r="E77">
-        <v>-9.790056246709181</v>
+        <v>-9.348486818653409</v>
       </c>
       <c r="F77">
-        <v>-2.573975409190175</v>
+        <v>-3.707041193761423</v>
       </c>
       <c r="G77">
-        <v>-2.174842381661269</v>
+        <v>2.024595118780864</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.061145383563022</v>
       </c>
       <c r="E78">
-        <v>-10.71757631903784</v>
+        <v>-9.512048587047808</v>
       </c>
       <c r="F78">
-        <v>-2.924494933847772</v>
+        <v>-3.935694619588768</v>
       </c>
       <c r="G78">
-        <v>-1.199891143045106</v>
+        <v>1.877704185106466</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.80302166495903</v>
       </c>
       <c r="E79">
-        <v>-11.29047444239601</v>
+        <v>-10.43544867374224</v>
       </c>
       <c r="F79">
-        <v>-3.362524847671914</v>
+        <v>-3.549123717193933</v>
       </c>
       <c r="G79">
-        <v>-0.9347360901378672</v>
+        <v>1.910612620677449</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.518846279217175</v>
       </c>
       <c r="E80">
-        <v>-12.69435124083721</v>
+        <v>-9.836538987856661</v>
       </c>
       <c r="F80">
-        <v>-2.864925377177654</v>
+        <v>-4.005313101222247</v>
       </c>
       <c r="G80">
-        <v>-0.06824040332573214</v>
+        <v>1.094621787980401</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.22180144819432</v>
       </c>
       <c r="E81">
-        <v>-11.68848499007698</v>
+        <v>-11.32810669021029</v>
       </c>
       <c r="F81">
-        <v>-2.880012432684841</v>
+        <v>-4.010635361785233</v>
       </c>
       <c r="G81">
-        <v>-0.7775092186272519</v>
+        <v>1.746827558753957</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.924348150857822</v>
       </c>
       <c r="E82">
-        <v>-13.29369701391189</v>
+        <v>-11.19765847570875</v>
       </c>
       <c r="F82">
-        <v>-3.258785084349721</v>
+        <v>-4.232273344078269</v>
       </c>
       <c r="G82">
-        <v>-0.8432947608341244</v>
+        <v>1.860896211428879</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.63576471207679</v>
       </c>
       <c r="E83">
-        <v>-14.20377359867627</v>
+        <v>-12.000524063334</v>
       </c>
       <c r="F83">
-        <v>-3.584220815683146</v>
+        <v>-4.180851609182087</v>
       </c>
       <c r="G83">
-        <v>-0.6694896611699396</v>
+        <v>1.732413637866421</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.373195607068027</v>
       </c>
       <c r="E84">
-        <v>-14.69554704522657</v>
+        <v>-12.88166107158697</v>
       </c>
       <c r="F84">
-        <v>-3.445589388987635</v>
+        <v>-4.382871366274622</v>
       </c>
       <c r="G84">
-        <v>-1.980114774843902</v>
+        <v>1.07041757487619</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.14933826113651</v>
       </c>
       <c r="E85">
-        <v>-13.73981005515702</v>
+        <v>-13.63882472179382</v>
       </c>
       <c r="F85">
-        <v>-3.862286357087481</v>
+        <v>-4.574399850210702</v>
       </c>
       <c r="G85">
-        <v>-1.146893027845506</v>
+        <v>1.992422913184575</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.9741784229270594</v>
       </c>
       <c r="E86">
-        <v>-15.67179674602944</v>
+        <v>-14.48002029673591</v>
       </c>
       <c r="F86">
-        <v>-4.16232931405549</v>
+        <v>-4.421536243167692</v>
       </c>
       <c r="G86">
-        <v>-0.7510414899625453</v>
+        <v>1.303938235572909</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.8646103906213731</v>
       </c>
       <c r="E87">
-        <v>-16.55315802769395</v>
+        <v>-15.27499893605532</v>
       </c>
       <c r="F87">
-        <v>-3.789813321383955</v>
+        <v>-4.82363986273242</v>
       </c>
       <c r="G87">
-        <v>-0.5760589444877685</v>
+        <v>1.651078500874878</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.82818911008984</v>
       </c>
       <c r="E88">
-        <v>-19.52818221068381</v>
+        <v>-16.31327269478318</v>
       </c>
       <c r="F88">
-        <v>-4.277819468986395</v>
+        <v>-5.014998531350924</v>
       </c>
       <c r="G88">
-        <v>-0.5686627050611445</v>
+        <v>1.382626077549063</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.87243237257477</v>
       </c>
       <c r="E89">
-        <v>-19.79602696223333</v>
+        <v>-17.92687835870557</v>
       </c>
       <c r="F89">
-        <v>-4.011935070240225</v>
+        <v>-5.013398125528716</v>
       </c>
       <c r="G89">
-        <v>0.006703630906765841</v>
+        <v>1.467101940283716</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.008040056337967</v>
       </c>
       <c r="E90">
-        <v>-21.33197588080407</v>
+        <v>-19.96716834129554</v>
       </c>
       <c r="F90">
-        <v>-3.831879474832919</v>
+        <v>-5.098113603078215</v>
       </c>
       <c r="G90">
-        <v>-0.4625829308350295</v>
+        <v>1.306969310043191</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.233696790269642</v>
       </c>
       <c r="E91">
-        <v>-22.88957964322246</v>
+        <v>-21.52113389059338</v>
       </c>
       <c r="F91">
-        <v>-3.884712747783472</v>
+        <v>-5.532186405819185</v>
       </c>
       <c r="G91">
-        <v>-0.1396364356589072</v>
+        <v>1.375644946512426</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.552405080129513</v>
       </c>
       <c r="E92">
-        <v>-23.69469211817445</v>
+        <v>-23.79723490578447</v>
       </c>
       <c r="F92">
-        <v>-4.570556225461711</v>
+        <v>-5.464382048797837</v>
       </c>
       <c r="G92">
-        <v>-0.6404216308924843</v>
+        <v>1.103832494897849</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.964905757031572</v>
       </c>
       <c r="E93">
-        <v>-27.3396874328177</v>
+        <v>-25.25866275355381</v>
       </c>
       <c r="F93">
-        <v>-4.684508102125617</v>
+        <v>-5.640818507022312</v>
       </c>
       <c r="G93">
-        <v>-0.7713687473489533</v>
+        <v>0.9978467074770137</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.4568573259063</v>
       </c>
       <c r="E94">
-        <v>-28.53272438174831</v>
+        <v>-27.32360619856796</v>
       </c>
       <c r="F94">
-        <v>-4.977948142525912</v>
+        <v>-5.936672410034364</v>
       </c>
       <c r="G94">
-        <v>0.1331184947530623</v>
+        <v>1.340230196133974</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.021461192623998</v>
       </c>
       <c r="E95">
-        <v>-30.90752438746828</v>
+        <v>-29.66796939509393</v>
       </c>
       <c r="F95">
-        <v>-4.852501011413357</v>
+        <v>-6.116024721516693</v>
       </c>
       <c r="G95">
-        <v>-1.698984575783641</v>
+        <v>0.6182000612710929</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.646678563606704</v>
       </c>
       <c r="E96">
-        <v>-33.40911985832961</v>
+        <v>-31.04617934754768</v>
       </c>
       <c r="F96">
-        <v>-5.524264728346213</v>
+        <v>-6.59377733740728</v>
       </c>
       <c r="G96">
-        <v>-0.6148911595359875</v>
+        <v>0.6743702311488953</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.303189838680685</v>
       </c>
       <c r="E97">
-        <v>-35.9069047578004</v>
+        <v>-35.22013180973241</v>
       </c>
       <c r="F97">
-        <v>-5.569411580166189</v>
+        <v>-6.682613942785707</v>
       </c>
       <c r="G97">
-        <v>-1.145459729064985</v>
+        <v>0.586121842480084</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.984351778001686</v>
       </c>
       <c r="E98">
-        <v>-38.40198176348741</v>
+        <v>-36.78235809635535</v>
       </c>
       <c r="F98">
-        <v>-5.999779095514436</v>
+        <v>-6.779317553388521</v>
       </c>
       <c r="G98">
-        <v>-1.090769851370344</v>
+        <v>0.08782207609724674</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.653976194387274</v>
       </c>
       <c r="E99">
-        <v>-42.7703335881534</v>
+        <v>-38.94416896570414</v>
       </c>
       <c r="F99">
-        <v>-5.578129318713251</v>
+        <v>-7.105896845921511</v>
       </c>
       <c r="G99">
-        <v>-1.506833773877704</v>
+        <v>0.3839066201754045</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.307237279033838</v>
       </c>
       <c r="E100">
-        <v>-43.98187517014178</v>
+        <v>-41.20892756076712</v>
       </c>
       <c r="F100">
-        <v>-5.488443636746954</v>
+        <v>-6.959759996372935</v>
       </c>
       <c r="G100">
-        <v>-2.177280817109369</v>
+        <v>-0.3703766533660905</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.897100785758131</v>
       </c>
       <c r="E101">
-        <v>-46.55994268282434</v>
+        <v>-44.04223794353684</v>
       </c>
       <c r="F101">
-        <v>-5.027279078097427</v>
+        <v>-6.873167438288692</v>
       </c>
       <c r="G101">
-        <v>-2.922671894573532</v>
+        <v>-0.9692344691648381</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.460357876637456</v>
       </c>
       <c r="E102">
-        <v>-49.64517544322702</v>
+        <v>-46.55675301652688</v>
       </c>
       <c r="F102">
-        <v>-5.899246770775882</v>
+        <v>-7.118748551992244</v>
       </c>
       <c r="G102">
-        <v>-2.958170188778899</v>
+        <v>-0.7738620084334665</v>
       </c>
     </row>
   </sheetData>
